--- a/assessment_forms/015_verbal_reasoning_assessment--assessment_forms.xlsx
+++ b/assessment_forms/015_verbal_reasoning_assessment--assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,7 +515,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -525,13 +525,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>What is your background information</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Background Information</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please provide your background information.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -548,33 +552,41 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>question 1</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Question 1 - What is your current role?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Describe your current role.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>question1_answer</t>
+          <t>question1_choice_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>question 1 answer</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Role - Executive</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Provide more details.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -589,38 +601,46 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>question1_choice_1</t>
+          <t>question1_choice_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>choice 1</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Role - Other</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Describe your role.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>question1_choice_2</t>
+          <t>question2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>choice 2</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Question 2 - What motivates you?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Describe what motivates you.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>yes</t>
@@ -635,18 +655,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>question1_choice_3</t>
+          <t>question2_choice_1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>choice 3</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Motivation - Financial</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>More details.</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -658,18 +682,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>question1_choice_4</t>
+          <t>question2_choice_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>choice 4</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Motivation - Other</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Describe your motivation.</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -681,38 +709,46 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>question2</t>
+          <t>question3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>question 2</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Question 3 - What is your work style?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Describe your work style.</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>question2_answer</t>
+          <t>question3_choice_1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>question 2 answer</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Style - Analytical</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Provide more details.</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -727,476 +763,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>question2_choice_1</t>
+          <t>question3_choice_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>choice 1</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Style - Other</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Describe your style.</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>question2_choice_2</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>choice 2</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>question3</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>question 3</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>question3_answer</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>question 3 answer</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>question3_choice_1</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>choice 1</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>question3_choice_2</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>choice 2</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>question4</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>question 4</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>question4_answer</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>question 4 answer</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>question4_choice_1</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>choice 1</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>question4_choice_2</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>choice 2</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>question5</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>question 5</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>question5_answer</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>question 5 answer</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>question5_choice_1</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>choice 1</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>question5_choice_2</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>choice 2</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>question5_choice_3</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>choice 3</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>question6</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>question 6</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>question6_answer</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>question 6 answer</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>question6_choice_1</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>choice 1</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>question6_choice_2</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>choice 2</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>question7</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>question 7</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>question7_answer</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>question 7 answer</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1213,12 +793,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1246,12 +826,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -1263,29 +843,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>director</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Director</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>question1_choice_2_choices</t>
+          <t>question1_choice_1_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>ceo</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>CEO</t>
         </is>
       </c>
     </row>
@@ -1297,80 +877,80 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>analyst</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Analyst</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>question1_choice_3_choices</t>
+          <t>question1_choice_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>engineer</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>Engineer</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>question1_choice_3_choices</t>
+          <t>question1_choice_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option6</t>
+          <t>consultant</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option6</t>
+          <t>Consultant</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>question1_choice_4_choices</t>
+          <t>question2_choice_1_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option7</t>
+          <t>personal_wealth</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option7</t>
+          <t>Personal wealth</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>question1_choice_4_choices</t>
+          <t>question2_choice_1_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option8</t>
+          <t>career_advancement</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option8</t>
+          <t>Career advancement</t>
         </is>
       </c>
     </row>
@@ -1382,29 +962,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option9</t>
+          <t>social_recognition</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option9</t>
+          <t>Social recognition</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>question2_choice_1_choices</t>
+          <t>question2_choice_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option10</t>
+          <t>creative_expression</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option10</t>
+          <t>Creative expression</t>
         </is>
       </c>
     </row>
@@ -1416,12 +996,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option11</t>
+          <t>social_impact</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option11</t>
+          <t>Social impact</t>
         </is>
       </c>
     </row>
@@ -1433,12 +1013,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option12</t>
+          <t>personal_satisfaction</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option12</t>
+          <t>Personal satisfaction</t>
         </is>
       </c>
     </row>
@@ -1450,12 +1030,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option13</t>
+          <t>data-driven</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option13</t>
+          <t>Data-driven</t>
         </is>
       </c>
     </row>
@@ -1467,29 +1047,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option14</t>
+          <t>strategic</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option14</t>
+          <t>Strategic</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>question3_choice_2_choices</t>
+          <t>question3_choice_1_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option15</t>
+          <t>advisory</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>option15</t>
+          <t>Advisory</t>
         </is>
       </c>
     </row>
@@ -1501,250 +1081,46 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option16</t>
+          <t>collaborative</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>option16</t>
+          <t>Collaborative</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>question4_choice_1_choices</t>
+          <t>question3_choice_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>option17</t>
+          <t>results-driven</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>option17</t>
+          <t>Results-driven</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>question4_choice_1_choices</t>
+          <t>question3_choice_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>option18</t>
+          <t>innovative</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>option18</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>question4_choice_2_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>option19</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>option19</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>question4_choice_2_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>option20</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>option20</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>question5_choice_1_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>option21</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>option21</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>question5_choice_1_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>option22</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>option22</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>question5_choice_2_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>option23</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>option23</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>question5_choice_2_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>option24</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>option24</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>question5_choice_3_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>option25</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>option25</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>question5_choice_3_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>option26</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>option26</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>question6_choice_1_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>option27</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>option27</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>question6_choice_1_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>option28</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>option28</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>question6_choice_2_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>option29</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>option29</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>question6_choice_2_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>option30</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>option30</t>
+          <t>Innovative</t>
         </is>
       </c>
     </row>
